--- a/artfynd/S 1630-2026 artfynd.xlsx
+++ b/artfynd/S 1630-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY45"/>
+  <dimension ref="A1:AZ45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17327970</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/53955843</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -986,6 +1001,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132334730</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1083,6 +1103,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/53955839</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1180,6 +1205,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/53955840</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1277,6 +1307,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/53955841</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1374,6 +1409,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88272491</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1479,6 +1519,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80487897</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1584,6 +1629,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80487910</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1685,6 +1735,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88272492</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1782,6 +1837,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88272460</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1890,6 +1950,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69580810</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1987,6 +2052,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88272461</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2089,6 +2159,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86762054</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2198,6 +2273,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114891979</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2318,6 +2398,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115295411</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2415,6 +2500,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86763348</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2512,6 +2602,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86763350</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2609,6 +2704,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86763334</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2706,6 +2806,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86763388</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2803,6 +2908,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86763425</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2900,6 +3010,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86763323</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2997,6 +3112,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86763445</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3094,6 +3214,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86763446</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3191,6 +3316,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86763447</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3288,6 +3418,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86763449</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3385,6 +3520,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86763450</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3482,6 +3622,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86763451</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3579,6 +3724,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86763453</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3676,6 +3826,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86763455</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3773,6 +3928,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86763457</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3870,6 +4030,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86763467</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3967,6 +4132,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86763470</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4064,6 +4234,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86763471</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4161,6 +4336,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86763474</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4258,6 +4438,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/53946694</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4355,6 +4540,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86763351</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4452,6 +4642,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86763352</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4549,6 +4744,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86763353</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4646,6 +4846,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86763354</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4747,6 +4952,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/53946695</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4844,6 +5054,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/53946696</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4941,6 +5156,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86763480</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5038,8 +5258,59 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86763481</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>